--- a/data/indicators_mapping.xlsx
+++ b/data/indicators_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Python Проект ДВ/notebook_mo расчеты июнь 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D393C-8E3E-014E-8915-5C299CC24CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A07354E-1719-AA4D-910A-D5E21FA0BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18780" xr2:uid="{FB484EE1-29E3-F74D-AC7F-A21463B4D79E}"/>
+    <workbookView xWindow="340" yWindow="600" windowWidth="33600" windowHeight="18780" xr2:uid="{FB484EE1-29E3-F74D-AC7F-A21463B4D79E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="194">
   <si>
     <t>Естественный прирост</t>
   </si>
@@ -578,21 +578,12 @@
     <t>registered_ip</t>
   </si>
   <si>
-    <t xml:space="preserve">ИП_Число зарегистрированных предприятий </t>
-  </si>
-  <si>
     <t>liquidated_ip</t>
   </si>
   <si>
-    <t>ИП_Число ликвидированных предприятий</t>
-  </si>
-  <si>
     <t>existing_ip</t>
   </si>
   <si>
-    <t>ИП_Число действующих предприятий</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -602,31 +593,31 @@
     <t>L_ci</t>
   </si>
   <si>
-    <t>КИ_Среднесписочная численность работников</t>
-  </si>
-  <si>
     <t>R/L_ci</t>
   </si>
   <si>
-    <t>КИ_Производительность труда: Выручка / ССЧ</t>
-  </si>
-  <si>
     <t>F/L_ci</t>
   </si>
   <si>
-    <t>КИ_Трудовооруженность: ОС/ССЧ</t>
-  </si>
-  <si>
     <t>W/L_ci</t>
   </si>
   <si>
-    <t>КИ_Средняя оплата труда: ОТ/ССЧ</t>
-  </si>
-  <si>
     <t>most_profitable</t>
   </si>
   <si>
     <t>ТОП прибыльных предприятий</t>
+  </si>
+  <si>
+    <t>Среднесписочная численность работников (ССЧ)</t>
+  </si>
+  <si>
+    <t>Число зарегистрированных ИП</t>
+  </si>
+  <si>
+    <t>Число ликвидированных ИП</t>
+  </si>
+  <si>
+    <t>Число действующих ИП</t>
   </si>
 </sst>
 </file>
@@ -691,9 +682,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -731,7 +722,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -837,7 +828,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -979,7 +970,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1758,71 +1749,71 @@
         <v>179</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data/indicators_mapping.xlsx
+++ b/data/indicators_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A07354E-1719-AA4D-910A-D5E21FA0BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A6FA63-304C-4448-A224-E112BC6803D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="340" yWindow="600" windowWidth="33600" windowHeight="18780" xr2:uid="{FB484EE1-29E3-F74D-AC7F-A21463B4D79E}"/>
   </bookViews>
@@ -605,9 +605,6 @@
     <t>most_profitable</t>
   </si>
   <si>
-    <t>ТОП прибыльных предприятий</t>
-  </si>
-  <si>
     <t>Среднесписочная численность работников (ССЧ)</t>
   </si>
   <si>
@@ -618,6 +615,9 @@
   </si>
   <si>
     <t>Число действующих ИП</t>
+  </si>
+  <si>
+    <t>ТОП предприятий по выручке</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1749,7 @@
         <v>179</v>
       </c>
       <c r="B81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -1757,7 +1757,7 @@
         <v>180</v>
       </c>
       <c r="B82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -1765,7 +1765,7 @@
         <v>181</v>
       </c>
       <c r="B83" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
@@ -1781,7 +1781,7 @@
         <v>184</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -1813,7 +1813,7 @@
         <v>188</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/data/indicators_mapping.xlsx
+++ b/data/indicators_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinamaleeva/Documents/Грант ДВ/Визуализация/project_DV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A6FA63-304C-4448-A224-E112BC6803D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDEAB7B-821C-0E4C-8478-B1AAE0760E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="600" windowWidth="33600" windowHeight="18780" xr2:uid="{FB484EE1-29E3-F74D-AC7F-A21463B4D79E}"/>
+    <workbookView xWindow="6520" yWindow="22660" windowWidth="21040" windowHeight="16700" xr2:uid="{FB484EE1-29E3-F74D-AC7F-A21463B4D79E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="204">
   <si>
     <t>Естественный прирост</t>
   </si>
@@ -98,9 +98,6 @@
     <t>social_payments</t>
   </si>
   <si>
-    <t>*1000</t>
-  </si>
-  <si>
     <t>Тысяча рублей</t>
   </si>
   <si>
@@ -383,48 +380,18 @@
     <t>expenses_s_business_per_person</t>
   </si>
   <si>
-    <t>не обрабатывала только 2008 и 2009 года</t>
-  </si>
-  <si>
     <t>Нет в файлах</t>
   </si>
   <si>
     <t>Занятость 2008-2016 и 2017-2024:</t>
   </si>
   <si>
-    <t>Migr</t>
-  </si>
-  <si>
-    <t>Popul</t>
-  </si>
-  <si>
-    <t>NatPopulGr</t>
-  </si>
-  <si>
-    <t>Birth</t>
-  </si>
-  <si>
-    <t>Mortal</t>
-  </si>
-  <si>
-    <t>Inv</t>
-  </si>
-  <si>
-    <t>Bud_Exp</t>
-  </si>
-  <si>
     <t>budget_revenues</t>
   </si>
   <si>
     <t>Доходы местного бюджета, фактически исполненные</t>
   </si>
   <si>
-    <t>Bud_Rev</t>
-  </si>
-  <si>
-    <t>Child</t>
-  </si>
-  <si>
     <t>registered</t>
   </si>
   <si>
@@ -488,15 +455,6 @@
     <t>HHI Оплата труда</t>
   </si>
   <si>
-    <t>Индекс Тейла Выручка</t>
-  </si>
-  <si>
-    <t>Индекс Тейла Основные средства</t>
-  </si>
-  <si>
-    <t>Индекс Тейла Оплата труда</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
@@ -618,6 +576,78 @@
   </si>
   <si>
     <t>ТОП предприятий по выручке</t>
+  </si>
+  <si>
+    <t>ssch</t>
+  </si>
+  <si>
+    <t>labor_productivity</t>
+  </si>
+  <si>
+    <t>capital_labor_ratio</t>
+  </si>
+  <si>
+    <t>avg_labor_cost</t>
+  </si>
+  <si>
+    <t>ti_w_revenues</t>
+  </si>
+  <si>
+    <t>ti_b_revenues</t>
+  </si>
+  <si>
+    <t>ti_w_fixed_assets</t>
+  </si>
+  <si>
+    <t>ti_b_fixed_assets</t>
+  </si>
+  <si>
+    <t>ti_w_wages</t>
+  </si>
+  <si>
+    <t>ti_b_wages</t>
+  </si>
+  <si>
+    <t>registered_orgs</t>
+  </si>
+  <si>
+    <t>liquidated_orgs</t>
+  </si>
+  <si>
+    <t>existing_orgs</t>
+  </si>
+  <si>
+    <t>existing_total</t>
+  </si>
+  <si>
+    <t>Индекс Тейла - выручка</t>
+  </si>
+  <si>
+    <t>Индекс Тейла - основные средства</t>
+  </si>
+  <si>
+    <t>Индекс Тейла - оплата труда</t>
+  </si>
+  <si>
+    <t>Индекс Тейла within - выручка</t>
+  </si>
+  <si>
+    <t>Индекс Тейла between - выручка</t>
+  </si>
+  <si>
+    <t>Индекс Тейла within - основные средства</t>
+  </si>
+  <si>
+    <t>Индекс Тейла between - основные средства</t>
+  </si>
+  <si>
+    <t>Индекс Тейла within - оплата труда</t>
+  </si>
+  <si>
+    <t>Индекс Тейла between - оплата труда</t>
+  </si>
+  <si>
+    <t>Всего организаций и ИП</t>
   </si>
 </sst>
 </file>
@@ -978,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE88A11F-59AC-F844-8A45-30137FD0BE64}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -987,29 +1017,23 @@
     <col min="4" max="4" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1017,7 +1041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1025,29 +1049,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1058,7 +1076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1069,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1077,7 +1095,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1085,7 +1103,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1093,727 +1111,806 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
         <v>58</v>
       </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
         <v>62</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
         <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
         <v>96</v>
       </c>
-      <c r="B48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
         <v>98</v>
       </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" t="s">
         <v>100</v>
       </c>
-      <c r="B50" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>102</v>
       </c>
-      <c r="B51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>103</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" t="s">
         <v>106</v>
       </c>
-      <c r="B53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
         <v>108</v>
       </c>
-      <c r="B54" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
         <v>110</v>
       </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>112</v>
-      </c>
-      <c r="B56" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E57" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>186</v>
+      </c>
+      <c r="B96" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B98" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>189</v>
+      </c>
+      <c r="B99" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>192</v>
+      </c>
+      <c r="B102" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>193</v>
+      </c>
+      <c r="B103" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1831,12 +1928,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
